--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260914.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>137,725</t>
+          <t>137,405</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.72%</t>
+          <t>26.36%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,685</t>
+          <t>99,560</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.05%</t>
+          <t>8.02%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>99,790</t>
+          <t>15,585</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.04%</t>
+          <t>7.59%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>50,765</t>
+          <t>50,645</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.17%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>121,005</t>
+          <t>120,725</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>5.48%</t>
         </is>
       </c>
     </row>
@@ -721,34 +721,34 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,550</t>
+          <t>59,410</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.71%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,735</t>
+          <t>18,183</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -765,73 +765,73 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>65,295</t>
+          <t>65,145</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,725</t>
+          <t>5,635</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,283</t>
+          <t>45,095</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>45,195</t>
+          <t>19,625</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>76,895</t>
+          <t>76,695</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>31,430</t>
+          <t>31,330</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>20,245</t>
+          <t>20,145</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -919,56 +919,56 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>50,845</t>
+          <t>50,725</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>19,490</t>
+          <t>26,478</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>26,478</t>
+          <t>19,390</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -990,24 +990,24 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>59,098</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,132 +1019,132 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>59,098</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>7,890</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>21,308</t>
+          <t>7,890</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>18,355</t>
+          <t>63,644,112</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>125,985</t>
+          <t>18,355</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>19,587</t>
+          <t>125,785</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51,016,112</t>
+          <t>19,587</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9,636</t>
+          <t>42,830</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1227,34 +1227,34 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>37,340</t>
+          <t>37,240</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,930</t>
+          <t>9,536</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>807,876</t>
+          <t>407,876</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1315,10 +1315,32 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,628,000</t>
+          <t>9,530,100</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>572,318</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
